--- a/Process_Docs/Risk_Sheet.xlsx
+++ b/Process_Docs/Risk_Sheet.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\iti\Clothing-Web-Portal\Process_Docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\QA\Process_Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36F5653C-267A-4BC6-9328-E83E6FC48BBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E723A1F1-4652-4A80-B9CC-611F0D06C915}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="11520" windowHeight="12360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="64">
   <si>
     <t>CATEGORIZATION</t>
   </si>
@@ -60,14 +60,190 @@
     <t>NEW RATING</t>
   </si>
   <si>
-    <t>dsds</t>
+    <t xml:space="preserve">Operational Risk/Internal </t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>high</t>
+  </si>
+  <si>
+    <t>increase mistakes in process in general
+-Idelay in I delivery</t>
+  </si>
+  <si>
+    <t>power outage</t>
+  </si>
+  <si>
+    <t>Flexible time to work</t>
+  </si>
+  <si>
+    <t>power outage for long time on consecutive time</t>
+  </si>
+  <si>
+    <t>Technical gaps between members and shortage</t>
+  </si>
+  <si>
+    <t>operational Risks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">high </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Make discount on items or orders exceed 1000 pounds
+</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>Human Errors Caused by Technical Skill Gaps in the Team</t>
+  </si>
+  <si>
+    <t>provide regular training sessions and knowledge sharing</t>
+  </si>
+  <si>
+    <t>External Risks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hiring new employees qualified to accelrate delivery and share experience and konwlege in the team </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> increase mistakes and delayed delivery</t>
+  </si>
+  <si>
+    <t>Regional Geopolitical conflict</t>
+  </si>
+  <si>
+    <t>Environmental Risks/External</t>
+  </si>
+  <si>
+    <t>the plan will move from hybrid to fully remote work</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Government cerfew announcement and movement restriction </t>
+  </si>
+  <si>
+    <t>Vulnerability to Cyberattacks</t>
+  </si>
+  <si>
+    <t>hiring a cyper security engineer</t>
+  </si>
+  <si>
+    <t>Customer data leakage and unauthorized access to data base</t>
+  </si>
+  <si>
+    <t>Time Constraints Due to Other Commitments (Projects, Deliverables, and ISTQB Exam Preparation)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Project Risk / Resource Risk </t>
+  </si>
+  <si>
+    <t>Reduce sprint scope and focus on high priority tasks.</t>
+  </si>
+  <si>
+    <t>Inconsistent output or delayed task delivery</t>
+  </si>
+  <si>
+    <t>Business Risk</t>
+  </si>
+  <si>
+    <t>Compliance of large number of our clients</t>
+  </si>
+  <si>
+    <t>PRIORITY</t>
+  </si>
+  <si>
+    <t>meduim</t>
+  </si>
+  <si>
+    <t>low/out of scope</t>
+  </si>
+  <si>
+    <t>medium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">low </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Operational Risk</t>
+  </si>
+  <si>
+    <t>Establish clear review guidelines and train admins to verify product details before approval.</t>
+  </si>
+  <si>
+    <t>Increase in customer complaints, return requests, or discovery of inaccurate product details after delivery</t>
+  </si>
+  <si>
+    <t>Acceptance of Incorrect Product Data by Admin or missing validation of product images</t>
+  </si>
+  <si>
+    <t>Operational Risk</t>
+  </si>
+  <si>
+    <t>Define review timelines assign responsibilities and monitor pending products regularly</t>
+  </si>
+  <si>
+    <t>Large number of pending products or seller complaints about approval time.</t>
+  </si>
+  <si>
+    <t>Delay in Product Approval by admin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Website supports engligh only </t>
+  </si>
+  <si>
+    <t>provide key website content in Arabic in addition to English</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Difficulty understanding of product details from non-English speaking users.</t>
+  </si>
+  <si>
+    <t>Technical Risk/
+ Security Risk</t>
+  </si>
+  <si>
+    <t>Impact\Prob</t>
+  </si>
+  <si>
+    <t>Low(1)</t>
+  </si>
+  <si>
+    <t>Med(2)</t>
+  </si>
+  <si>
+    <t>High(3)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Tw Cen MT"/>
+        <family val="2"/>
+      </rPr>
+      <t>User</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Tw Cen MT"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Dissatisfaction Due to Limited Payment Options (Cash on Delivery Only)
+NOTE:out of current project scope</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -76,51 +252,43 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="9"/>
-      <color theme="0"/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
       <name val="Tw Cen MT"/>
       <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <color theme="0"/>
-      <name val="Tw Cen MT"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="8"/>
-      <color theme="0"/>
-      <name val="Tw Cen MT"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="Tw Cen MT"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
+      <sz val="14"/>
       <color rgb="FF000000"/>
       <name val="Tw Cen MT"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Tw Cen MT"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF7C98B6"/>
+      <name val="Tw Cen MT"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="14"/>
       <color theme="0"/>
       <name val="Tw Cen MT"/>
       <family val="2"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF7C98B6"/>
-      <name val="Tw Cen MT"/>
-      <family val="2"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -145,8 +313,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="8">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -259,55 +433,139 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7C98B6"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7C98B6"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF7C98B6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7C98B6"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7C98B6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -590,195 +848,423 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A3:I16"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:N14"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="18.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="44.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.36328125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="16.08984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="38.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="46.90625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="37.36328125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="11.90625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="14.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.81640625" style="1"/>
+  </cols>
   <sheetData>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2" t="s">
+      <c r="B1" s="20"/>
+      <c r="C1" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" s="20"/>
+      <c r="I1" s="21"/>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A2" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="G2" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="14" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" s="4" customFormat="1" ht="36" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="2">
+        <v>6</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>13</v>
+      </c>
       <c r="G3" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I3" s="3"/>
+      <c r="K3" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="L3" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="M3" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="N3" s="17" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" s="4" customFormat="1" ht="72" x14ac:dyDescent="0.35">
+      <c r="A4" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4" s="7">
+        <v>6</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="I4" s="8"/>
+      <c r="J4" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="K4" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L4" s="18">
+        <v>1</v>
+      </c>
+      <c r="M4" s="18">
         <v>2</v>
       </c>
-      <c r="H3" s="3"/>
-      <c r="I3" s="4"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" s="5" t="s">
+      <c r="N4" s="18">
         <v>3</v>
       </c>
-      <c r="B4" s="6" t="s">
+    </row>
+    <row r="5" spans="1:14" s="4" customFormat="1" ht="36" x14ac:dyDescent="0.35">
+      <c r="A5" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="6">
+        <v>6</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I5" s="5"/>
+      <c r="K5" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L5" s="18">
+        <v>2</v>
+      </c>
+      <c r="M5" s="18">
         <v>4</v>
       </c>
-      <c r="C4" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" s="6" t="s">
+      <c r="N5" s="18">
         <v>6</v>
       </c>
-      <c r="E4" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="H4" s="6" t="s">
+    </row>
+    <row r="6" spans="1:14" s="4" customFormat="1" ht="72" x14ac:dyDescent="0.35">
+      <c r="A6" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="7">
         <v>9</v>
       </c>
-      <c r="I4" s="7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5" s="8"/>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="9"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6" s="10"/>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="11"/>
-      <c r="H6" s="11"/>
-      <c r="I6" s="11"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8" s="12"/>
-      <c r="B8" s="12"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10" s="12"/>
-      <c r="B10" s="12"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11" s="13"/>
-      <c r="B11" s="13"/>
-      <c r="C11" s="13"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="9"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A12" s="12"/>
-      <c r="B12" s="12"/>
-      <c r="C12" s="12"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13" s="8"/>
-      <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="9"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A14" s="12"/>
-      <c r="B14" s="12"/>
-      <c r="C14" s="12"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="11"/>
-      <c r="H14" s="11"/>
-      <c r="I14" s="11"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15" s="8"/>
-      <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="9"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A16" s="10"/>
-      <c r="B16" s="10"/>
-      <c r="C16" s="10"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="11"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="11"/>
-      <c r="H16" s="11"/>
-      <c r="I16" s="11"/>
+      <c r="D6" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I6" s="8"/>
+      <c r="K6" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L6" s="18">
+        <v>3</v>
+      </c>
+      <c r="M6" s="18">
+        <v>6</v>
+      </c>
+      <c r="N6" s="18">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" s="4" customFormat="1" ht="54" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" s="2">
+        <v>9</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="I7" s="3"/>
+    </row>
+    <row r="8" spans="1:14" s="4" customFormat="1" ht="72" x14ac:dyDescent="0.35">
+      <c r="A8" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="7">
+        <v>9</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="I8" s="8"/>
+      <c r="K8" s="16"/>
+      <c r="L8" s="18"/>
+      <c r="M8" s="18"/>
+      <c r="N8" s="18"/>
+    </row>
+    <row r="9" spans="1:14" s="4" customFormat="1" ht="37" x14ac:dyDescent="0.35">
+      <c r="A9" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C9" s="10">
+        <v>9</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I9" s="3"/>
+    </row>
+    <row r="10" spans="1:14" ht="54" x14ac:dyDescent="0.35">
+      <c r="A10" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C10" s="7">
+        <v>2</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="I10" s="8"/>
+    </row>
+    <row r="11" spans="1:14" ht="54" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11" s="2">
+        <v>6</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="I11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" ht="54" x14ac:dyDescent="0.35">
+      <c r="A12" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C12" s="7">
+        <v>4</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="I12" s="8"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A13" s="9"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A14" s="11"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="C3:F3"/>
-    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:I1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>